--- a/resources/housing_substation_template.xlsx
+++ b/resources/housing_substation_template.xlsx
@@ -3537,7 +3537,7 @@
     <col width="10" customWidth="1" min="22" max="27"/>
     <col width="10.28515625" customWidth="1" min="28" max="28"/>
     <col width="10" customWidth="1" min="29" max="33"/>
-    <col hidden="1" min="53" max="54"/>
+    <col hidden="1" width="13" customWidth="1" min="53" max="54"/>
     <col width="2.7109375" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
@@ -3704,6 +3704,8 @@
           <t>제철회관</t>
         </is>
       </c>
+      <c r="X3" s="211" t="n"/>
+      <c r="Y3" s="212" t="n"/>
       <c r="AC3" s="172" t="n"/>
       <c r="AF3" s="172" t="n"/>
       <c r="AI3" s="172" t="n"/>
@@ -5182,7 +5184,7 @@
       <c r="AD16" s="212" t="n"/>
       <c r="AE16" s="174" t="inlineStr">
         <is>
-          <t xml:space="preserve">휴먼센터 </t>
+          <t>휴먼센터</t>
         </is>
       </c>
       <c r="AF16" s="211" t="n"/>
